--- a/export/vba/GMWO-Export.xlsx
+++ b/export/vba/GMWO-Export.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A65BBB0-B200-409F-BE30-ADC8B1523D4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7D587CA6-EBDF-4AF1-A852-24BA46AD4C4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37880" yWindow="-3790" windowWidth="28800" windowHeight="15450" xr2:uid="{5BC9FD85-612A-444D-8FC0-340DC3C97F82}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{5F5099A6-B547-43AC-9494-042A0BBF6E80}"/>
   </bookViews>
   <sheets>
     <sheet name="Start here" sheetId="5" r:id="rId1"/>
@@ -1244,7 +1244,7 @@
         <xdr:cNvPr id="2" name="btn_RunExport">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{35708F56-9170-8C5E-B1CB-B3EEA365EAD5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8748BE52-8564-5B2C-6013-90FBBAC53391}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1306,20 +1306,20 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>22225</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1838325</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>352425</xdr:rowOff>
+      <xdr:rowOff>355600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="TestToken" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="btn_TestToken">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{12CD3E2A-2A68-0E93-793A-F2A714D7970D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DD419F2-2C17-468C-600C-5E5C8C33481F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1381,20 +1381,20 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1838325</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>349250</xdr:rowOff>
+      <xdr:rowOff>355600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="SelfTest_BuildBody" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="4" name="btn_SelfTest_BuildBody">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F8D23660-B4B1-CA69-82FD-8E2A070E7F04}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4D1904DD-3173-0AE0-1537-4A2F0A3FF2E8}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1456,20 +1456,20 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1838325</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>349250</xdr:rowOff>
+      <xdr:rowOff>355600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="SelfTest_RunAll" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="5" name="btn_SelfTest_RunAll">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6A7B09C-FB61-0001-D98A-C14476471024}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{55FBDFCB-1300-FFD9-8EDF-68035007BD87}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1531,20 +1531,20 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1838325</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>349250</xdr:rowOff>
+      <xdr:rowOff>355600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="ClearToken" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="6" name="btn_ClearToken">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D72869D7-4576-CE82-C374-0BC8F3423DCE}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1EF755DE-CD28-5674-113C-1EDDD4F50CF1}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1606,20 +1606,20 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1838325</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>349250</xdr:rowOff>
+      <xdr:rowOff>355600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="ClearData" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="7" name="btn_ClearData">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68E63532-9967-8FF6-ECC3-EAE2A24565B1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97D603E7-420F-6C08-9042-FDFD04F470A0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1681,20 +1681,20 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>25400</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
       <xdr:colOff>1838325</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>349250</xdr:rowOff>
+      <xdr:rowOff>355600</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="ClearLog" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="8" name="btn_ClearLog">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{064E9A39-7AD6-C9C5-B377-ABF74235787D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{690D832F-750F-519B-10BE-5248CFCDBA9E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1755,43 +1755,43 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C957792F-4C77-44EA-A112-77BA6C458242}" name="tblIndicators" displayName="tblIndicators" ref="A9:A11" totalsRowShown="0">
-  <autoFilter ref="A9:A11" xr:uid="{C957792F-4C77-44EA-A112-77BA6C458242}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{249231CA-160E-4089-864B-824F291A1310}" name="tblIndicators" displayName="tblIndicators" ref="A9:A11" totalsRowShown="0">
+  <autoFilter ref="A9:A11" xr:uid="{249231CA-160E-4089-864B-824F291A1310}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{1AD663B5-BA1F-443F-9559-004FBEB42FC1}" name="Indicator"/>
+    <tableColumn id="1" xr3:uid="{33CFC7BA-5B1F-42C7-914E-60FC1FADF7B7}" name="Indicator"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DFAA7D4A-233C-4D1C-B7AE-FB4ED50668E7}" name="tblLocations" displayName="tblLocations" ref="C9:C11" totalsRowShown="0">
-  <autoFilter ref="C9:C11" xr:uid="{DFAA7D4A-233C-4D1C-B7AE-FB4ED50668E7}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DA7B6A61-3979-4EC2-A42F-1D70338C44F9}" name="tblLocations" displayName="tblLocations" ref="C9:C11" totalsRowShown="0">
+  <autoFilter ref="C9:C11" xr:uid="{DA7B6A61-3979-4EC2-A42F-1D70338C44F9}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{E54219D7-A261-4EA0-B59F-D61DDCD23628}" name="Location"/>
+    <tableColumn id="1" xr3:uid="{CD100909-718E-4BE6-959E-54287F39E9E0}" name="Location"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E5A8FD67-D565-4ABE-8467-93BFC526B868}" name="tblTransformations" displayName="tblTransformations" ref="E9:E11" totalsRowShown="0">
-  <autoFilter ref="E9:E11" xr:uid="{E5A8FD67-D565-4ABE-8467-93BFC526B868}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{E900813C-F5FB-4151-950B-6130761B914F}" name="tblTransformations" displayName="tblTransformations" ref="E9:E11" totalsRowShown="0">
+  <autoFilter ref="E9:E11" xr:uid="{E900813C-F5FB-4151-950B-6130761B914F}"/>
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{4C824302-4C29-4A85-822A-D3431911A137}" name="Transformation"/>
+    <tableColumn id="1" xr3:uid="{25B2D26C-3B7D-491E-8B14-C1DE9CC38834}" name="Transformation"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{BA2DF06A-39CF-456C-834D-DABA7AFFD83E}" name="tblSeries" displayName="tblSeries" ref="G9:J10" totalsRowShown="0" tableBorderDxfId="0">
-  <autoFilter ref="G9:J10" xr:uid="{BA2DF06A-39CF-456C-834D-DABA7AFFD83E}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{95577214-334C-4DA1-982F-3C1FB5646FD9}" name="tblSeries" displayName="tblSeries" ref="G9:J10" totalsRowShown="0" tableBorderDxfId="0">
+  <autoFilter ref="G9:J10" xr:uid="{95577214-334C-4DA1-982F-3C1FB5646FD9}"/>
   <tableColumns count="4">
-    <tableColumn id="1" xr3:uid="{DDB8D6B1-4A72-41F1-89BD-0060C45494E5}" name="Indicator"/>
-    <tableColumn id="2" xr3:uid="{ABA0AAD4-3ED6-4625-88DB-BE4C2A9BB124}" name="Location"/>
-    <tableColumn id="3" xr3:uid="{945D8AF6-E21A-4015-B502-42AB40F49452}" name="Transformation"/>
-    <tableColumn id="4" xr3:uid="{E7B100BA-B17F-408C-8A0E-4B0CA9BF49D9}" name="ValueType"/>
+    <tableColumn id="1" xr3:uid="{D62AD3D9-F21F-4C16-9497-5D4BB629500F}" name="Indicator"/>
+    <tableColumn id="2" xr3:uid="{A9A5AE8E-714D-4FE0-8CB7-DE9AEDE36DF4}" name="Location"/>
+    <tableColumn id="3" xr3:uid="{24B743F3-44D1-4CD2-B1E8-31796991B2C3}" name="Transformation"/>
+    <tableColumn id="4" xr3:uid="{E33CBD4A-1529-40F0-8441-B0ADE8BADC7B}" name="ValueType"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2113,7 +2113,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5864BBF-208F-4DCE-9B84-8F79F30FA7EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{683F66E4-06EB-4DB3-ABC0-C1172132C74F}">
   <dimension ref="A1:B145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3203,7 +3203,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C194493B-A725-45F5-9FA7-B337613EED3E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E5653C5-251C-40FA-879A-8FC5A940603A}">
   <dimension ref="A1:C26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3376,18 +3376,18 @@
   </sheetData>
   <sheetProtection sheet="1" scenarios="1" formatCells="0"/>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B9" xr:uid="{2A801F22-B9FA-4946-8E44-DC0EE4EA1EFA}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B9" xr:uid="{F6E08759-0609-42EC-A4FA-A151E6E6365E}">
       <formula1>"Variable,Residual"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10" xr:uid="{88CC891B-91B7-405E-BB41-E52A20FC0DE2}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B10" xr:uid="{3EA2C02A-434F-425C-A999-B2604C0A1E04}">
       <formula1>"Default,DefaultExtended,Classic_v,Classic_h,Skinny,DatabankCompatible,DatabankCompatibleStacked"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{2B9679C8-3B2E-4F50-9EB9-FB47B1DD7071}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B11" xr:uid="{A690FC1A-6F24-4769-9DCF-88E93E4C8167}">
       <formula1>"TRUE,FALSE"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C10" location="'Start here'!A21" tooltip="Jump to the list of output formats on the Start here sheet" display="'Start here'!A21" xr:uid="{8A2E32FA-679F-4B20-B62A-79B5DC4A6C63}"/>
+    <hyperlink ref="C10" location="'Start here'!A21" tooltip="Jump to the list of output formats on the Start here sheet" display="'Start here'!A21" xr:uid="{F045DD74-DB1E-4E95-917F-D432B530D0B8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3395,7 +3395,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E83954B0-BD90-47AD-96FC-E584E9D7D173}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72B72E5A-E19B-49E0-98B0-EFB081967018}">
   <dimension ref="A1:L209"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -4116,18 +4116,18 @@
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10:E209 I10:I209" xr:uid="{68854EBA-1399-4DD9-BCB8-1708D4CF2550}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E10:E209 I10:I209" xr:uid="{FE8A6BD6-5CC2-4034-B53C-1A856569E883}">
       <formula1>"L,PY,DY,GR,P,D"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J209" xr:uid="{35E03149-4477-4A7C-A190-6B905537E4C0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J10:J209" xr:uid="{627DEAB6-C693-409F-9430-E339BD50B0D4}">
       <formula1>"Variable,Residual"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10:C209 H10:H209" xr:uid="{1D0CCC12-0C8F-4CB6-8F13-51AFD9919C1D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C10:C209 H10:H209" xr:uid="{A9BB4C9B-671C-42FE-9386-047FF67670AE}">
       <formula1>loc_Codes</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="A4" location="'Start here'!A12" tooltip="Jump to the list of transformations on the Start here sheet" display="'Start here'!A12" xr:uid="{185803E2-8012-4BA1-831A-76254C55DFAF}"/>
+    <hyperlink ref="A4" location="'Start here'!A12" tooltip="Jump to the list of transformations on the Start here sheet" display="'Start here'!A12" xr:uid="{A256A7E3-7F79-4FC6-B3D7-A6C62E9508E3}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="4">
@@ -4140,7 +4140,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E9AB3C-0137-4D84-AA62-09F204CEA337}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BC5A6085-2ADF-4066-83F4-792B89FC1EF0}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4155,7 +4155,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47DDB975-738D-4946-A53D-E65B6D8A3E07}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BAF920A-C0E4-40FE-947F-73F4BF452EFC}">
   <dimension ref="A1:D1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
